--- a/MeasureCentralTendency/DA103_S6_Datafile_Practice.xlsx
+++ b/MeasureCentralTendency/DA103_S6_Datafile_Practice.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LEARN_NIIT\Assignment\Sprint-6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\LEARN_NIIT\Gitcode\JijuDataAnalyticsCodes\MeasureCentralTendency\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A874C475-47A1-44C0-A3A3-D645AC0D1662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6F416D-5B5D-44BF-A6A0-D1CA0D18B067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11964" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,38 +25,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Task 3'!$R$1:$S$366</definedName>
     <definedName name="_xlchart.v1.0" hidden="1">'Task 1'!$O$1:$O$2</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">'Task 1'!$O$3:$O$262</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">'Task 2'!$O$2</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">'Task 2'!$O$3:$O$190</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">'Task 2'!$P$2</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">'Task 2'!$P$3:$P$190</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">'Task 2'!$Q$2</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">'Task 2'!$Q$3:$Q$190</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">'Task 3'!$R$2</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">'Task 3'!$R$3:$R$353</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">'Task 3'!$S$2</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">'Task 3'!$S$3:$S$353</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">'Task 3'!$R$2</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">'Task 3'!$R$3:$R$353</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">'Task 3'!$S$2</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">'Task 3'!$S$3:$S$353</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">'Task 1'!$P$1:$P$2</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">'Task 3'!$R$2</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">'Task 3'!$R$3:$R$353</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">'Task 3'!$S$2</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">'Task 3'!$S$3:$S$353</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">'Task 3'!$R$2</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">'Task 3'!$R$3:$R$353</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">'Task 3'!$S$2</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">'Task 3'!$S$3:$S$353</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">'Task 3'!$R$2</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">'Task 3'!$R$3:$R$353</definedName>
     <definedName name="_xlchart.v1.3" hidden="1">'Task 1'!$P$3:$P$262</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">'Task 3'!$S$2</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">'Task 3'!$S$3:$S$353</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">'Task 3'!$R$2</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">'Task 3'!$R$3:$R$353</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">'Task 3'!$S$2</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">'Task 3'!$S$3:$S$353</definedName>
-    <definedName name="_xlchart.v1.36" hidden="1">'Task 3'!$R$2</definedName>
-    <definedName name="_xlchart.v1.37" hidden="1">'Task 3'!$R$3:$R$353</definedName>
-    <definedName name="_xlchart.v1.38" hidden="1">'Task 3'!$S$2</definedName>
-    <definedName name="_xlchart.v1.39" hidden="1">'Task 3'!$S$3:$S$353</definedName>
     <definedName name="_xlchart.v1.4" hidden="1">'Task 2'!$O$2</definedName>
     <definedName name="_xlchart.v1.5" hidden="1">'Task 2'!$O$3:$O$190</definedName>
     <definedName name="_xlchart.v1.6" hidden="1">'Task 2'!$P$2</definedName>
@@ -615,17 +589,17 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.11</cx:f>
+        <cx:f>_xlchart.v1.5</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.13</cx:f>
+        <cx:f>_xlchart.v1.7</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.15</cx:f>
+        <cx:f>_xlchart.v1.9</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -662,7 +636,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{FFA7AE8F-5E0F-42CA-A948-471826FF59B4}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.10</cx:f>
+              <cx:f>_xlchart.v1.4</cx:f>
               <cx:v>Morning</cx:v>
             </cx:txData>
           </cx:tx>
@@ -704,7 +678,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{0EA6B810-771A-4F2F-B1FD-FEE4E7578617}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.12</cx:f>
+              <cx:f>_xlchart.v1.6</cx:f>
               <cx:v>Afternoon</cx:v>
             </cx:txData>
           </cx:tx>
@@ -745,7 +719,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{4FE1562C-FA33-4480-998D-27541AFD54D9}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.14</cx:f>
+              <cx:f>_xlchart.v1.8</cx:f>
               <cx:v>Evening</cx:v>
             </cx:txData>
           </cx:tx>
@@ -831,12 +805,12 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.29</cx:f>
+        <cx:f>_xlchart.v1.11</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.31</cx:f>
+        <cx:f>_xlchart.v1.13</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -873,7 +847,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{7EE24172-81C8-4732-A204-E2FCBA2D29D5}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.28</cx:f>
+              <cx:f>_xlchart.v1.10</cx:f>
               <cx:v>Not Holiday</cx:v>
             </cx:txData>
           </cx:tx>
@@ -915,7 +889,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{21BC2683-658A-4D9E-9538-1D4ED19670DE}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.30</cx:f>
+              <cx:f>_xlchart.v1.12</cx:f>
               <cx:v>Holiday</cx:v>
             </cx:txData>
           </cx:tx>
@@ -4102,7 +4076,21 @@
               <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>   None clearly marked → distributions are within expected ranges.</a:t>
+            <a:t>   None clearly marked shows</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" b="1" kern="1200" baseline="0">
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> that</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" b="1" kern="1200">
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> distributions are within expected ranges.</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
